--- a/elite-data/manifest-templates/EL_template_AssayWholeGenomeSequencingTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayWholeGenomeSequencingTemplate.xlsx
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="106">
   <si>
     <t>Filename</t>
   </si>
@@ -390,7 +390,7 @@
     <t>MetaboLights</t>
   </si>
   <si>
-    <t>sac-seq</t>
+    <t>Qiagen Rneasy Extraction Kit</t>
   </si>
   <si>
     <t>Metabolomics Workbench</t>
@@ -399,7 +399,7 @@
     <t>PCRfree</t>
   </si>
   <si>
-    <t>Smart-seq1</t>
+    <t>sac-seq</t>
   </si>
   <si>
     <t>MGnify</t>
@@ -408,7 +408,7 @@
     <t>polyAselection</t>
   </si>
   <si>
-    <t>Smart-seq2</t>
+    <t>Smart-seq1</t>
   </si>
   <si>
     <t>NCBI Gene</t>
@@ -417,43 +417,49 @@
     <t>proximity ligation</t>
   </si>
   <si>
+    <t>Smart-seq2</t>
+  </si>
+  <si>
+    <t>rRNAdepletion</t>
+  </si>
+  <si>
     <t>Smart-seq4</t>
+  </si>
+  <si>
+    <t>snIsoSeq</t>
+  </si>
+  <si>
+    <t>SMRTbell</t>
+  </si>
+  <si>
+    <t>SPLITseq</t>
+  </si>
+  <si>
+    <t>TruSeq</t>
+  </si>
+  <si>
+    <t>STARRSeq</t>
+  </si>
+  <si>
+    <t>Ultralow Methyl-Seq</t>
   </si>
   <si>
     <t>PRIDE</t>
   </si>
   <si>
-    <t>rRNAdepletion</t>
-  </si>
-  <si>
-    <t>SMRTbell</t>
+    <t>SureCell</t>
   </si>
   <si>
     <t>SRA</t>
   </si>
   <si>
-    <t>snIsoSeq</t>
+    <t>totalRNA</t>
   </si>
   <si>
-    <t>TruSeq</t>
+    <t>Synapse</t>
   </si>
   <si>
     <t>UniProt</t>
-  </si>
-  <si>
-    <t>SPLITseq</t>
-  </si>
-  <si>
-    <t>Ultralow Methyl-Seq</t>
-  </si>
-  <si>
-    <t>STARRSeq</t>
-  </si>
-  <si>
-    <t>SureCell</t>
-  </si>
-  <si>
-    <t>totalRNA</t>
   </si>
 </sst>
 </file>
@@ -27839,6 +27845,12 @@
     </row>
   </sheetData>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="P2:P1000">
+      <formula1>Sheet2!$P$2:$P$23</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
+      <formula1>Sheet2!$H$2:$H$27</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="S2:S1000">
       <formula1>Sheet2!$S$2:$S$9</formula1>
     </dataValidation>
@@ -27853,12 +27865,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
       <formula1>Sheet2!$V$2:$V$8</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
-      <formula1>Sheet2!$H$2:$H$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="P2:P1000">
-      <formula1>Sheet2!$P$2:$P$22</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="J2:J1000">
       <formula1>Sheet2!$J$2:$J$9</formula1>
@@ -28241,57 +28247,82 @@
     </row>
     <row r="19">
       <c r="H19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="O19" s="7" t="s">
+      <c r="P19" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="P19" s="7" t="s">
+    </row>
+    <row r="20">
+      <c r="H20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O20" s="7" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="H20" s="7" t="s">
+      <c r="P20" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="O20" s="7" t="s">
+    </row>
+    <row r="21">
+      <c r="H21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="O21" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="P20" s="7" t="s">
+      <c r="P21" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="21">
-      <c r="H21" s="7" t="s">
+    <row r="22">
+      <c r="H22" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="O22" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="O21" s="7" t="s">
+      <c r="P22" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="P21" s="7" t="s">
+    </row>
+    <row r="23">
+      <c r="H23" s="7" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="O22" s="7" t="s">
+      <c r="O23" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="P22" s="7" t="s">
+      <c r="P23" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23">
-      <c r="O23" s="7" t="s">
+    <row r="24">
+      <c r="H24" s="7" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="24">
       <c r="O24" s="7" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="25">
+      <c r="H25" s="7" t="s">
+        <v>104</v>
+      </c>
       <c r="O25" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" s="7" t="s">
         <v>65</v>
       </c>
     </row>

--- a/elite-data/manifest-templates/EL_template_AssayWholeGenomeSequencingTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayWholeGenomeSequencingTemplate.xlsx
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="107">
   <si>
     <t>Filename</t>
   </si>
@@ -342,7 +342,7 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>GENCODEv38 GRCh38</t>
+    <t>GENCODEv38</t>
   </si>
   <si>
     <t>total RNA minus rRNA</t>
@@ -369,31 +369,31 @@
     <t>multiome</t>
   </si>
   <si>
-    <t>IEDB</t>
+    <t>GRCh38</t>
   </si>
   <si>
     <t>MULTIseq</t>
   </si>
   <si>
-    <t>ImmPort</t>
+    <t>IEDB</t>
   </si>
   <si>
     <t>Omni-ATAC</t>
   </si>
   <si>
-    <t>MassIVE</t>
+    <t>ImmPort</t>
   </si>
   <si>
     <t>Qiagen PreAnalytiX PAXgene Blood miRNA Kit</t>
   </si>
   <si>
-    <t>MetaboLights</t>
+    <t>MassIVE</t>
   </si>
   <si>
     <t>Qiagen Rneasy Extraction Kit</t>
   </si>
   <si>
-    <t>Metabolomics Workbench</t>
+    <t>MetaboLights</t>
   </si>
   <si>
     <t>PCRfree</t>
@@ -402,7 +402,7 @@
     <t>sac-seq</t>
   </si>
   <si>
-    <t>MGnify</t>
+    <t>Metabolomics Workbench</t>
   </si>
   <si>
     <t>polyAselection</t>
@@ -411,13 +411,16 @@
     <t>Smart-seq1</t>
   </si>
   <si>
-    <t>NCBI Gene</t>
+    <t>MGnify</t>
   </si>
   <si>
     <t>proximity ligation</t>
   </si>
   <si>
     <t>Smart-seq2</t>
+  </si>
+  <si>
+    <t>NCBI Gene</t>
   </si>
   <si>
     <t>rRNAdepletion</t>
@@ -444,16 +447,16 @@
     <t>Ultralow Methyl-Seq</t>
   </si>
   <si>
+    <t>SureCell</t>
+  </si>
+  <si>
     <t>PRIDE</t>
   </si>
   <si>
-    <t>SureCell</t>
+    <t>totalRNA</t>
   </si>
   <si>
     <t>SRA</t>
-  </si>
-  <si>
-    <t>totalRNA</t>
   </si>
   <si>
     <t>Synapse</t>
@@ -27852,9 +27855,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="P2:P1000">
       <formula1>Sheet2!$P$2:$P$23</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
-      <formula1>Sheet2!$H$2:$H$27</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="S2:S1000">
       <formula1>Sheet2!$S$2:$S$9</formula1>
     </dataValidation>
@@ -27869,6 +27869,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
       <formula1>Sheet2!$V$2:$V$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
+      <formula1>Sheet2!$H$2:$H$28</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="J2:J1000">
       <formula1>Sheet2!$J$2:$J$9</formula1>
@@ -28251,51 +28254,51 @@
     </row>
     <row r="19">
       <c r="H19" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="O19" s="7" t="s">
-        <v>92</v>
+      <c r="O20" s="7" t="s">
+        <v>95</v>
       </c>
-      <c r="P19" s="7" t="s">
-        <v>93</v>
+      <c r="P20" s="7" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="20">
-      <c r="H20" s="7" t="s">
+    <row r="21">
+      <c r="H21" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="O20" s="7" t="s">
-        <v>94</v>
+      <c r="O21" s="7" t="s">
+        <v>97</v>
       </c>
-      <c r="P20" s="7" t="s">
-        <v>95</v>
+      <c r="P21" s="7" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="21">
-      <c r="H21" s="7" t="s">
+    <row r="22">
+      <c r="H22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="O21" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="H22" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="O22" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="7" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="O23" s="7" t="s">
         <v>101</v>
@@ -28327,6 +28330,11 @@
     </row>
     <row r="27">
       <c r="H27" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" s="7" t="s">
         <v>65</v>
       </c>
     </row>

--- a/elite-data/manifest-templates/EL_template_AssayWholeGenomeSequencingTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayWholeGenomeSequencingTemplate.xlsx
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="106">
   <si>
     <t>Filename</t>
   </si>
@@ -321,7 +321,7 @@
     <t>stranded</t>
   </si>
   <si>
-    <t>singleEnd pairedEnd</t>
+    <t>Unknown</t>
   </si>
   <si>
     <t>GenBank</t>
@@ -337,9 +337,6 @@
   </si>
   <si>
     <t>NEBNext</t>
-  </si>
-  <si>
-    <t>Unknown</t>
   </si>
   <si>
     <t>GENCODEv38</t>
@@ -27855,6 +27852,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="P2:P1000">
       <formula1>Sheet2!$P$2:$P$23</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
+      <formula1>Sheet2!$V$2:$V$7</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="S2:S1000">
       <formula1>Sheet2!$S$2:$S$9</formula1>
     </dataValidation>
@@ -27866,9 +27866,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="R2:R1000">
       <formula1>Sheet2!$R$2:$R$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
-      <formula1>Sheet2!$V$2:$V$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
       <formula1>Sheet2!$H$2:$H$28</formula1>
@@ -28124,41 +28121,38 @@
         <v>64</v>
       </c>
       <c r="S8" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="V8" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="H9" s="7" t="s">
+      <c r="I9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="O9" s="7" t="s">
+      <c r="P9" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="S9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="S9" s="7" t="s">
+    </row>
+    <row r="10">
+      <c r="H10" s="7" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="H10" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="I10" s="7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P10" s="7" t="s">
         <v>32</v>
@@ -28166,10 +28160,10 @@
     </row>
     <row r="11">
       <c r="H11" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P11" s="7" t="s">
         <v>38</v>
@@ -28177,10 +28171,10 @@
     </row>
     <row r="12">
       <c r="H12" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>42</v>
@@ -28188,79 +28182,79 @@
     </row>
     <row r="13">
       <c r="H13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>32</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
       <c r="H14" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O14" s="7" t="s">
         <v>38</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
       <c r="H15" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>42</v>
       </c>
       <c r="P15" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" s="7" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="H16" s="7" t="s">
+      <c r="O16" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="O16" s="7" t="s">
+      <c r="P16" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P16" s="7" t="s">
+    </row>
+    <row r="17">
+      <c r="H17" s="7" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="H17" s="7" t="s">
+      <c r="O17" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="O17" s="7" t="s">
+      <c r="P17" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="P17" s="7" t="s">
+    </row>
+    <row r="18">
+      <c r="H18" s="7" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="H18" s="7" t="s">
+      <c r="O18" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="O18" s="7" t="s">
+      <c r="P18" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="P18" s="7" t="s">
+    </row>
+    <row r="19">
+      <c r="H19" s="7" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="H19" s="7" t="s">
+      <c r="O19" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="O19" s="7" t="s">
+      <c r="P19" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="20">
@@ -28268,10 +28262,10 @@
         <v>32</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21">
@@ -28279,10 +28273,10 @@
         <v>38</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22">
@@ -28290,10 +28284,10 @@
         <v>42</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23">
@@ -28301,41 +28295,41 @@
         <v>54</v>
       </c>
       <c r="O23" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="P23" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="H24" s="7" t="s">
+      <c r="O24" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="O24" s="7" t="s">
+    </row>
+    <row r="25">
+      <c r="H25" s="7" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="H25" s="7" t="s">
+      <c r="O25" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="O25" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="H26" s="7" t="s">
+    </row>
+    <row r="27">
+      <c r="H27" s="7" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="27">
-      <c r="H27" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
     <row r="28">
       <c r="H28" s="7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/elite-data/manifest-templates/EL_template_AssayWholeGenomeSequencingTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayWholeGenomeSequencingTemplate.xlsx
@@ -240,7 +240,7 @@
     <t>forward</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>Broad Single Cell Portal</t>
@@ -258,7 +258,7 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>dbGAP</t>
@@ -321,7 +321,7 @@
     <t>stranded</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>GenBank</t>
